--- a/artfynd/A 13589-2025 artfynd.xlsx
+++ b/artfynd/A 13589-2025 artfynd.xlsx
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123657283</v>
+        <v>123657206</v>
       </c>
       <c r="B4" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,14 +951,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>7, Dlr</t>
+          <t>Dammsjön, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530198</v>
+        <v>530170</v>
       </c>
       <c r="R4" t="n">
-        <v>6713857</v>
+        <v>6713806</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123657303</v>
+        <v>123657235</v>
       </c>
       <c r="B5" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1058,14 +1058,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>10, Dlr</t>
+          <t>Dammsjön, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530297</v>
+        <v>530191</v>
       </c>
       <c r="R5" t="n">
-        <v>6713863</v>
+        <v>6713819</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1125,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123657291</v>
+        <v>123657303</v>
       </c>
       <c r="B6" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,14 +1165,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>8, Dlr</t>
+          <t>Dammsjön, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530192</v>
+        <v>530297</v>
       </c>
       <c r="R6" t="n">
-        <v>6713864</v>
+        <v>6713863</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1232,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123657297</v>
+        <v>123657247</v>
       </c>
       <c r="B7" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1272,14 +1272,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>9, Dlr</t>
+          <t>Dammsjön, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>530270</v>
+        <v>530215</v>
       </c>
       <c r="R7" t="n">
-        <v>6713894</v>
+        <v>6713789</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1339,10 +1339,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123657206</v>
+        <v>123657283</v>
       </c>
       <c r="B8" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,14 +1379,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2, Dlr</t>
+          <t>Dammsjön, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>530170</v>
+        <v>530198</v>
       </c>
       <c r="R8" t="n">
-        <v>6713806</v>
+        <v>6713857</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1446,10 +1446,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123657235</v>
+        <v>123657263</v>
       </c>
       <c r="B9" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,14 +1486,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>3, Dlr</t>
+          <t>Dammsjön, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>530191</v>
+        <v>530259</v>
       </c>
       <c r="R9" t="n">
-        <v>6713819</v>
+        <v>6713823</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123657247</v>
+        <v>123657275</v>
       </c>
       <c r="B10" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1593,14 +1593,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>4, Dlr</t>
+          <t>Dammsjön, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>530215</v>
+        <v>530242</v>
       </c>
       <c r="R10" t="n">
-        <v>6713789</v>
+        <v>6713837</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1660,10 +1660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123657275</v>
+        <v>123657291</v>
       </c>
       <c r="B11" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1700,14 +1700,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>6, Dlr</t>
+          <t>Dammsjön, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>530242</v>
+        <v>530192</v>
       </c>
       <c r="R11" t="n">
-        <v>6713837</v>
+        <v>6713864</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1767,10 +1767,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123657263</v>
+        <v>123657297</v>
       </c>
       <c r="B12" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,14 +1807,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>5, Dlr</t>
+          <t>Dammsjön, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>530259</v>
+        <v>530270</v>
       </c>
       <c r="R12" t="n">
-        <v>6713823</v>
+        <v>6713894</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1877,7 +1877,7 @@
         <v>123663311</v>
       </c>
       <c r="B13" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 13589-2025 artfynd.xlsx
+++ b/artfynd/A 13589-2025 artfynd.xlsx
@@ -911,7 +911,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123657206</v>
+        <v>123657235</v>
       </c>
       <c r="B4" t="n">
         <v>98396</v>
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530170</v>
+        <v>530191</v>
       </c>
       <c r="R4" t="n">
-        <v>6713806</v>
+        <v>6713819</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123657235</v>
+        <v>123657206</v>
       </c>
       <c r="B5" t="n">
         <v>98396</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530191</v>
+        <v>530170</v>
       </c>
       <c r="R5" t="n">
-        <v>6713819</v>
+        <v>6713806</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>

--- a/artfynd/A 13589-2025 artfynd.xlsx
+++ b/artfynd/A 13589-2025 artfynd.xlsx
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123657235</v>
+        <v>123657206</v>
       </c>
       <c r="B4" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530191</v>
+        <v>530170</v>
       </c>
       <c r="R4" t="n">
-        <v>6713819</v>
+        <v>6713806</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123657206</v>
+        <v>123657235</v>
       </c>
       <c r="B5" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530170</v>
+        <v>530191</v>
       </c>
       <c r="R5" t="n">
-        <v>6713806</v>
+        <v>6713819</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1125,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123657303</v>
+        <v>123657275</v>
       </c>
       <c r="B6" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530297</v>
+        <v>530242</v>
       </c>
       <c r="R6" t="n">
-        <v>6713863</v>
+        <v>6713837</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1232,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123657247</v>
+        <v>123657297</v>
       </c>
       <c r="B7" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>530215</v>
+        <v>530270</v>
       </c>
       <c r="R7" t="n">
-        <v>6713789</v>
+        <v>6713894</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1339,10 +1339,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123657283</v>
+        <v>123657303</v>
       </c>
       <c r="B8" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>530198</v>
+        <v>530297</v>
       </c>
       <c r="R8" t="n">
-        <v>6713857</v>
+        <v>6713863</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1449,7 +1449,7 @@
         <v>123657263</v>
       </c>
       <c r="B9" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123657275</v>
+        <v>123657291</v>
       </c>
       <c r="B10" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>530242</v>
+        <v>530192</v>
       </c>
       <c r="R10" t="n">
-        <v>6713837</v>
+        <v>6713864</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1660,10 +1660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123657291</v>
+        <v>123657283</v>
       </c>
       <c r="B11" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,10 +1704,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>530192</v>
+        <v>530198</v>
       </c>
       <c r="R11" t="n">
-        <v>6713864</v>
+        <v>6713857</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1767,10 +1767,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123657297</v>
+        <v>123657247</v>
       </c>
       <c r="B12" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>530270</v>
+        <v>530215</v>
       </c>
       <c r="R12" t="n">
-        <v>6713894</v>
+        <v>6713789</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1877,7 +1877,7 @@
         <v>123663311</v>
       </c>
       <c r="B13" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 13589-2025 artfynd.xlsx
+++ b/artfynd/A 13589-2025 artfynd.xlsx
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123657206</v>
+        <v>123657275</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530170</v>
+        <v>530242</v>
       </c>
       <c r="R4" t="n">
-        <v>6713806</v>
+        <v>6713837</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123657235</v>
+        <v>123657303</v>
       </c>
       <c r="B5" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530191</v>
+        <v>530297</v>
       </c>
       <c r="R5" t="n">
-        <v>6713819</v>
+        <v>6713863</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1125,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123657275</v>
+        <v>123657297</v>
       </c>
       <c r="B6" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>530242</v>
+        <v>530270</v>
       </c>
       <c r="R6" t="n">
-        <v>6713837</v>
+        <v>6713894</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1232,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123657297</v>
+        <v>123657235</v>
       </c>
       <c r="B7" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,10 +1276,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>530270</v>
+        <v>530191</v>
       </c>
       <c r="R7" t="n">
-        <v>6713894</v>
+        <v>6713819</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1339,10 +1339,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123657303</v>
+        <v>123657283</v>
       </c>
       <c r="B8" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>530297</v>
+        <v>530198</v>
       </c>
       <c r="R8" t="n">
-        <v>6713863</v>
+        <v>6713857</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1449,7 +1449,7 @@
         <v>123657263</v>
       </c>
       <c r="B9" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123657291</v>
+        <v>123657206</v>
       </c>
       <c r="B10" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>530192</v>
+        <v>530170</v>
       </c>
       <c r="R10" t="n">
-        <v>6713864</v>
+        <v>6713806</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1660,10 +1660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123657283</v>
+        <v>123657291</v>
       </c>
       <c r="B11" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,10 +1704,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>530198</v>
+        <v>530192</v>
       </c>
       <c r="R11" t="n">
-        <v>6713857</v>
+        <v>6713864</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1770,7 +1770,7 @@
         <v>123657247</v>
       </c>
       <c r="B12" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>123663311</v>
       </c>
       <c r="B13" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 13589-2025 artfynd.xlsx
+++ b/artfynd/A 13589-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1997,6 +1997,810 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123947069</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92271</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Dammsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>530243</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6713862</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123959146</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92271</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Dammsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>530158</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6713794</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Isabelle  Hammarström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Isabelle  Hammarström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123947276</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92271</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Dammsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>530238</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6713878</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123949543</v>
+      </c>
+      <c r="B17" t="n">
+        <v>105520</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Dammsjön, Dammsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>530234</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6713944</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123949312</v>
+      </c>
+      <c r="B18" t="n">
+        <v>105520</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Dammsjön, Dammsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>530246</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6713945</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123947765</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91435</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Dammsjön, Dammsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>530184</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6713858</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>123949466</v>
+      </c>
+      <c r="B20" t="n">
+        <v>105520</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Dammsjön, Dammsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>530237</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6713938</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13589-2025 artfynd.xlsx
+++ b/artfynd/A 13589-2025 artfynd.xlsx
@@ -2213,7 +2213,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123949543</v>
+        <v>123949466</v>
       </c>
       <c r="B16" t="n">
         <v>105117</v>
@@ -2253,10 +2253,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>530234</v>
+        <v>530237</v>
       </c>
       <c r="R16" t="n">
-        <v>6713944</v>
+        <v>6713938</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2325,10 +2325,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123959146</v>
+        <v>123947765</v>
       </c>
       <c r="B17" t="n">
-        <v>92293</v>
+        <v>91457</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2337,52 +2337,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Dammsjön, Dlr</t>
+          <t>Dammsjön, Dammsjön, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>530158</v>
+        <v>530184</v>
       </c>
       <c r="R17" t="n">
-        <v>6713794</v>
+        <v>6713858</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2409,40 +2398,49 @@
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Isabelle  Hammarström</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Isabelle  Hammarström</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123947276</v>
+        <v>123949543</v>
       </c>
       <c r="B18" t="n">
-        <v>92293</v>
+        <v>105117</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2455,43 +2453,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Dammsjön, Dlr</t>
+          <t>Dammsjön, Dammsjön, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>530238</v>
+        <v>530234</v>
       </c>
       <c r="R18" t="n">
-        <v>6713878</v>
+        <v>6713944</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2523,7 +2512,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2533,7 +2522,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2560,10 +2549,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123947765</v>
+        <v>123949312</v>
       </c>
       <c r="B19" t="n">
-        <v>91457</v>
+        <v>105117</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2572,25 +2561,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2600,10 +2589,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>530184</v>
+        <v>530246</v>
       </c>
       <c r="R19" t="n">
-        <v>6713858</v>
+        <v>6713945</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2635,7 +2624,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2645,7 +2634,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2672,10 +2661,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123949312</v>
+        <v>123947069</v>
       </c>
       <c r="B20" t="n">
-        <v>105117</v>
+        <v>92293</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2688,34 +2677,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Dammsjön, Dammsjön, Dlr</t>
+          <t>Dammsjön, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>530246</v>
+        <v>530243</v>
       </c>
       <c r="R20" t="n">
-        <v>6713945</v>
+        <v>6713862</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2747,7 +2745,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2757,7 +2755,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2784,7 +2782,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123947069</v>
+        <v>123959146</v>
       </c>
       <c r="B21" t="n">
         <v>92293</v>
@@ -2819,7 +2817,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2827,19 +2825,21 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Dammsjön, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>530243</v>
+        <v>530158</v>
       </c>
       <c r="R21" t="n">
-        <v>6713862</v>
+        <v>6713794</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2866,49 +2866,40 @@
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Isabelle  Hammarström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+          <t>Isabelle  Hammarström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123949466</v>
+        <v>123947276</v>
       </c>
       <c r="B22" t="n">
-        <v>105117</v>
+        <v>92293</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2921,34 +2912,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Dammsjön, Dammsjön, Dlr</t>
+          <t>Dammsjön, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>530237</v>
+        <v>530238</v>
       </c>
       <c r="R22" t="n">
-        <v>6713938</v>
+        <v>6713878</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 13589-2025 artfynd.xlsx
+++ b/artfynd/A 13589-2025 artfynd.xlsx
@@ -2213,10 +2213,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123949466</v>
+        <v>123959146</v>
       </c>
       <c r="B16" t="n">
-        <v>105117</v>
+        <v>92293</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2229,37 +2229,48 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Dammsjön, Dammsjön, Dlr</t>
+          <t>Dammsjön, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>530237</v>
+        <v>530158</v>
       </c>
       <c r="R16" t="n">
-        <v>6713938</v>
+        <v>6713794</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2286,49 +2297,40 @@
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Isabelle  Hammarström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+          <t>Isabelle  Hammarström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123947765</v>
+        <v>123947276</v>
       </c>
       <c r="B17" t="n">
-        <v>91457</v>
+        <v>92293</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2337,38 +2339,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Dammsjön, Dammsjön, Dlr</t>
+          <t>Dammsjön, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>530184</v>
+        <v>530238</v>
       </c>
       <c r="R17" t="n">
-        <v>6713858</v>
+        <v>6713878</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2400,7 +2411,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2410,7 +2421,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2437,7 +2448,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123949543</v>
+        <v>123949312</v>
       </c>
       <c r="B18" t="n">
         <v>105117</v>
@@ -2477,10 +2488,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>530234</v>
+        <v>530246</v>
       </c>
       <c r="R18" t="n">
-        <v>6713944</v>
+        <v>6713945</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2512,7 +2523,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2522,7 +2533,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2549,7 +2560,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123949312</v>
+        <v>123949543</v>
       </c>
       <c r="B19" t="n">
         <v>105117</v>
@@ -2589,10 +2600,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>530246</v>
+        <v>530234</v>
       </c>
       <c r="R19" t="n">
-        <v>6713945</v>
+        <v>6713944</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2624,7 +2635,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2634,7 +2645,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2661,10 +2672,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123947069</v>
+        <v>123949466</v>
       </c>
       <c r="B20" t="n">
-        <v>92293</v>
+        <v>105117</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2677,43 +2688,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Dammsjön, Dlr</t>
+          <t>Dammsjön, Dammsjön, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>530243</v>
+        <v>530237</v>
       </c>
       <c r="R20" t="n">
-        <v>6713862</v>
+        <v>6713938</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2745,7 +2747,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2755,7 +2757,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2782,10 +2784,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123959146</v>
+        <v>123947765</v>
       </c>
       <c r="B21" t="n">
-        <v>92293</v>
+        <v>91457</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2794,52 +2796,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Dammsjön, Dlr</t>
+          <t>Dammsjön, Dammsjön, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>530158</v>
+        <v>530184</v>
       </c>
       <c r="R21" t="n">
-        <v>6713794</v>
+        <v>6713858</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2866,37 +2857,46 @@
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Isabelle  Hammarström</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Isabelle  Hammarström</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123947276</v>
+        <v>123947069</v>
       </c>
       <c r="B22" t="n">
         <v>92293</v>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2945,10 +2945,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>530238</v>
+        <v>530243</v>
       </c>
       <c r="R22" t="n">
-        <v>6713878</v>
+        <v>6713862</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 13589-2025 artfynd.xlsx
+++ b/artfynd/A 13589-2025 artfynd.xlsx
@@ -2213,7 +2213,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123959146</v>
+        <v>123947276</v>
       </c>
       <c r="B16" t="n">
         <v>92293</v>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2256,21 +2256,19 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Dammsjön, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>530158</v>
+        <v>530238</v>
       </c>
       <c r="R16" t="n">
-        <v>6713794</v>
+        <v>6713878</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2297,40 +2295,49 @@
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Isabelle  Hammarström</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Isabelle  Hammarström</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123947276</v>
+        <v>123949543</v>
       </c>
       <c r="B17" t="n">
-        <v>92293</v>
+        <v>105117</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2343,43 +2350,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Dammsjön, Dlr</t>
+          <t>Dammsjön, Dammsjön, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>530238</v>
+        <v>530234</v>
       </c>
       <c r="R17" t="n">
-        <v>6713878</v>
+        <v>6713944</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2411,7 +2409,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2421,7 +2419,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2448,10 +2446,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123949312</v>
+        <v>123947765</v>
       </c>
       <c r="B18" t="n">
-        <v>105117</v>
+        <v>91457</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2460,25 +2458,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2488,10 +2486,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>530246</v>
+        <v>530184</v>
       </c>
       <c r="R18" t="n">
-        <v>6713945</v>
+        <v>6713858</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2523,7 +2521,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2533,7 +2531,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2560,10 +2558,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123949543</v>
+        <v>123947069</v>
       </c>
       <c r="B19" t="n">
-        <v>105117</v>
+        <v>92293</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2576,34 +2574,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Dammsjön, Dammsjön, Dlr</t>
+          <t>Dammsjön, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>530234</v>
+        <v>530243</v>
       </c>
       <c r="R19" t="n">
-        <v>6713944</v>
+        <v>6713862</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2635,7 +2642,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2645,7 +2652,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2784,10 +2791,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123947765</v>
+        <v>123949312</v>
       </c>
       <c r="B21" t="n">
-        <v>91457</v>
+        <v>105117</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2796,25 +2803,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2824,10 +2831,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>530184</v>
+        <v>530246</v>
       </c>
       <c r="R21" t="n">
-        <v>6713858</v>
+        <v>6713945</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2859,7 +2866,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2869,7 +2876,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2896,7 +2903,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123947069</v>
+        <v>123959146</v>
       </c>
       <c r="B22" t="n">
         <v>92293</v>
@@ -2931,7 +2938,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2939,19 +2946,21 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Dammsjön, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>530243</v>
+        <v>530158</v>
       </c>
       <c r="R22" t="n">
-        <v>6713862</v>
+        <v>6713794</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2978,39 +2987,30 @@
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Isabelle  Hammarström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+          <t>Isabelle  Hammarström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 13589-2025 artfynd.xlsx
+++ b/artfynd/A 13589-2025 artfynd.xlsx
@@ -2213,10 +2213,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123947276</v>
+        <v>123949466</v>
       </c>
       <c r="B16" t="n">
-        <v>92293</v>
+        <v>105117</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2229,43 +2229,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Dammsjön, Dlr</t>
+          <t>Dammsjön, Dammsjön, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>530238</v>
+        <v>530237</v>
       </c>
       <c r="R16" t="n">
-        <v>6713878</v>
+        <v>6713938</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2297,7 +2288,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2307,7 +2298,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2334,10 +2325,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123949543</v>
+        <v>123947765</v>
       </c>
       <c r="B17" t="n">
-        <v>105117</v>
+        <v>91457</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2346,25 +2337,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2374,10 +2365,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>530234</v>
+        <v>530184</v>
       </c>
       <c r="R17" t="n">
-        <v>6713944</v>
+        <v>6713858</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2409,7 +2400,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2419,7 +2410,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2446,10 +2437,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123947765</v>
+        <v>123949312</v>
       </c>
       <c r="B18" t="n">
-        <v>91457</v>
+        <v>105117</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2458,25 +2449,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2486,10 +2477,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>530184</v>
+        <v>530246</v>
       </c>
       <c r="R18" t="n">
-        <v>6713858</v>
+        <v>6713945</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2521,7 +2512,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2531,7 +2522,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2558,10 +2549,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123947069</v>
+        <v>123949543</v>
       </c>
       <c r="B19" t="n">
-        <v>92293</v>
+        <v>105117</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2574,43 +2565,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Dammsjön, Dlr</t>
+          <t>Dammsjön, Dammsjön, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>530243</v>
+        <v>530234</v>
       </c>
       <c r="R19" t="n">
-        <v>6713862</v>
+        <v>6713944</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2642,7 +2624,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2652,7 +2634,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2679,10 +2661,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123949466</v>
+        <v>123947276</v>
       </c>
       <c r="B20" t="n">
-        <v>105117</v>
+        <v>92293</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2695,34 +2677,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Dammsjön, Dammsjön, Dlr</t>
+          <t>Dammsjön, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>530237</v>
+        <v>530238</v>
       </c>
       <c r="R20" t="n">
-        <v>6713938</v>
+        <v>6713878</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2754,7 +2745,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2764,7 +2755,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2791,10 +2782,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123949312</v>
+        <v>123947069</v>
       </c>
       <c r="B21" t="n">
-        <v>105117</v>
+        <v>92293</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2807,34 +2798,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Dammsjön, Dammsjön, Dlr</t>
+          <t>Dammsjön, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>530246</v>
+        <v>530243</v>
       </c>
       <c r="R21" t="n">
-        <v>6713945</v>
+        <v>6713862</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 13589-2025 artfynd.xlsx
+++ b/artfynd/A 13589-2025 artfynd.xlsx
@@ -2213,10 +2213,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123949466</v>
+        <v>123947069</v>
       </c>
       <c r="B16" t="n">
-        <v>105117</v>
+        <v>92293</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2229,34 +2229,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Dammsjön, Dammsjön, Dlr</t>
+          <t>Dammsjön, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>530237</v>
+        <v>530243</v>
       </c>
       <c r="R16" t="n">
-        <v>6713938</v>
+        <v>6713862</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2288,7 +2297,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2298,7 +2307,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2325,10 +2334,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123947765</v>
+        <v>123959146</v>
       </c>
       <c r="B17" t="n">
-        <v>91457</v>
+        <v>92293</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2337,41 +2346,52 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Dammsjön, Dammsjön, Dlr</t>
+          <t>Dammsjön, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>530184</v>
+        <v>530158</v>
       </c>
       <c r="R17" t="n">
-        <v>6713858</v>
+        <v>6713794</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2398,46 +2418,37 @@
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:46</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Isabelle  Hammarström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
+          <t>Isabelle  Hammarström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123949312</v>
+        <v>123949543</v>
       </c>
       <c r="B18" t="n">
         <v>105117</v>
@@ -2477,10 +2488,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>530246</v>
+        <v>530234</v>
       </c>
       <c r="R18" t="n">
-        <v>6713945</v>
+        <v>6713944</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2512,7 +2523,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2522,7 +2533,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2549,10 +2560,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123949543</v>
+        <v>123947765</v>
       </c>
       <c r="B19" t="n">
-        <v>105117</v>
+        <v>91457</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2561,25 +2572,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2589,10 +2600,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>530234</v>
+        <v>530184</v>
       </c>
       <c r="R19" t="n">
-        <v>6713944</v>
+        <v>6713858</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2624,7 +2635,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2634,7 +2645,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2661,10 +2672,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123947276</v>
+        <v>123949312</v>
       </c>
       <c r="B20" t="n">
-        <v>92293</v>
+        <v>105117</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2677,43 +2688,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Dammsjön, Dlr</t>
+          <t>Dammsjön, Dammsjön, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>530238</v>
+        <v>530246</v>
       </c>
       <c r="R20" t="n">
-        <v>6713878</v>
+        <v>6713945</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2745,7 +2747,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2755,7 +2757,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2782,7 +2784,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123947069</v>
+        <v>123947276</v>
       </c>
       <c r="B21" t="n">
         <v>92293</v>
@@ -2817,7 +2819,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2831,10 +2833,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>530243</v>
+        <v>530238</v>
       </c>
       <c r="R21" t="n">
-        <v>6713862</v>
+        <v>6713878</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2866,7 +2868,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2876,7 +2878,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2903,10 +2905,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123959146</v>
+        <v>123949466</v>
       </c>
       <c r="B22" t="n">
-        <v>92293</v>
+        <v>105117</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2919,48 +2921,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Dammsjön, Dlr</t>
+          <t>Dammsjön, Dammsjön, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>530158</v>
+        <v>530237</v>
       </c>
       <c r="R22" t="n">
-        <v>6713794</v>
+        <v>6713938</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2987,30 +2978,39 @@
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Isabelle  Hammarström</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Isabelle  Hammarström</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
